--- a/data/trans_orig/P5B_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42650</t>
+          <t>42722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47188</t>
+          <t>47192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94158</t>
+          <t>93900</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98357</t>
+          <t>98356</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60490</t>
+          <t>60779</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124247</t>
+          <t>123437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131035</t>
+          <t>131167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56619</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63309</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66667</t>
+          <t>66673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120469</t>
+          <t>120795</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129273</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62161</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67009</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131201</t>
+          <t>130903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137754</t>
+          <t>137767</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>102004</t>
+          <t>101968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109183</t>
+          <t>109182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101565</t>
+          <t>101745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108782</t>
+          <t>108840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>206838</t>
+          <t>206700</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>216464</t>
+          <t>216606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>83146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88913</t>
+          <t>89044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>89380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>95413</t>
+          <t>95396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>175075</t>
+          <t>175406</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>183436</t>
+          <t>183560</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>477003</t>
+          <t>475156</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>490538</t>
+          <t>489746</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>505845</t>
+          <t>504686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>517976</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>985522</t>
+          <t>987183</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1004624</t>
+          <t>1005296</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>30966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55265</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48108</t>
+          <t>47457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53698</t>
+          <t>53683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52156</t>
+          <t>51683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102583</t>
+          <t>102501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110585</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>47288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108732</t>
+          <t>108748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44495</t>
+          <t>44509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>100030</t>
+          <t>99757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>40929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90367</t>
+          <t>90575</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111726</t>
+          <t>111699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118090</t>
+          <t>118361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232896</t>
+          <t>232793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>237813</t>
+          <t>237808</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111207</t>
+          <t>110953</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>238567</t>
+          <t>239674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>460636</t>
+          <t>459603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>522941</t>
+          <t>523240</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>532817</t>
+          <t>532717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>986914</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1001509</t>
+          <t>1001007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42948</t>
+          <t>42932</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>44064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50644</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89417</t>
+          <t>89225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>95894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>64591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69593</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75577</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143093</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149009</t>
+          <t>149376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>583</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39777</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>85404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>90438</t>
+          <t>90433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29158</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>32385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63484</t>
+          <t>63567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>108789</t>
+          <t>109669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114955</t>
+          <t>114947</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115843</t>
+          <t>115294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>227172</t>
+          <t>227389</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233948</t>
+          <t>233522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126433</t>
+          <t>125637</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265126</t>
+          <t>264145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>507805</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>517360</t>
+          <t>517515</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>558749</t>
+          <t>558539</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>567061</t>
+          <t>567203</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1070614</t>
+          <t>1071278</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1083167</t>
+          <t>1083334</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>83411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116231</t>
+          <t>103726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45965</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126638</t>
+          <t>126642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138321</t>
+          <t>150826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253655</t>
+          <t>253678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61908</t>
+          <t>62164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66617</t>
+          <t>66622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119193</t>
+          <t>118987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124348</t>
+          <t>124276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69324</t>
+          <t>68781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>139891</t>
+          <t>139785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>147294</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>73007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42669</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99330</t>
+          <t>99543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>120421</t>
+          <t>120201</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147874</t>
+          <t>148368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154511</t>
+          <t>154470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>271067</t>
+          <t>271124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278100</t>
+          <t>278404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151604</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282808</t>
+          <t>281894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134992</t>
+          <t>155409</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>555073</t>
+          <t>544043</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>662056</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>743268</t>
+          <t>744313</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>755109</t>
+          <t>754731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1290737</t>
+          <t>1270320</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1413035</t>
+          <t>1413051</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
